--- a/p6_deployment/data/italy/missing/data_understanding/df_match_miss.xlsx
+++ b/p6_deployment/data/italy/missing/data_understanding/df_match_miss.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>tYVGfTo</t>
+          <t>tYVGfTo2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>tYVGfTo</t>
+          <t>tYVGfTo2</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>ryme5Xs</t>
+          <t>ryme5Xs1</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -16366,7 +16366,7 @@
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -16648,7 +16648,7 @@
       <c r="AX56" t="inlineStr"/>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
@@ -16948,7 +16948,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -17228,7 +17228,7 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>KdJpmvQ</t>
+          <t>KdJpmvQM</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -17518,7 +17518,7 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>EDkXRoL</t>
+          <t>EDkXRoLT</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
@@ -18398,7 +18398,7 @@
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -19304,7 +19304,12 @@
           <t>14.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Fourneau F.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>Stadio Giuseppe Meazza (San Siro)
@@ -19543,7 +19548,7 @@
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
@@ -19553,7 +19558,7 @@
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
@@ -19833,7 +19838,7 @@
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
@@ -19843,7 +19848,7 @@
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
@@ -20123,7 +20128,7 @@
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
@@ -20133,7 +20138,7 @@
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
@@ -20421,7 +20426,7 @@
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
@@ -20431,7 +20436,7 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -20711,7 +20716,7 @@
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
@@ -20721,7 +20726,7 @@
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -21009,7 +21014,7 @@
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
@@ -21019,7 +21024,7 @@
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -21299,7 +21304,7 @@
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
@@ -21309,7 +21314,7 @@
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
@@ -21589,7 +21594,7 @@
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>EDkXRoL</t>
+          <t>EDkXRoLT</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
@@ -21599,7 +21604,7 @@
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -21879,7 +21884,7 @@
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
@@ -21889,7 +21894,7 @@
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -22169,7 +22174,7 @@
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
@@ -22179,7 +22184,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -22459,7 +22464,7 @@
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
@@ -22469,7 +22474,7 @@
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -22749,7 +22754,7 @@
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
@@ -22759,7 +22764,7 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -23039,7 +23044,7 @@
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
@@ -23049,7 +23054,7 @@
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -23329,7 +23334,7 @@
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
@@ -23339,7 +23344,7 @@
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
@@ -23619,7 +23624,7 @@
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
@@ -23629,7 +23634,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -23909,7 +23914,7 @@
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
@@ -23919,7 +23924,7 @@
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -24207,7 +24212,7 @@
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
@@ -24217,7 +24222,7 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -24498,7 +24503,7 @@
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
@@ -24508,7 +24513,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -24789,7 +24794,7 @@
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
@@ -24799,7 +24804,7 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -25088,7 +25093,7 @@
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
@@ -25098,7 +25103,7 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
